--- a/data/trending_integrated_20261019_14.xlsx
+++ b/data/trending_integrated_20261019_14.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F2" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2" t="n">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20590513292</v>
+        <v>20605406252</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -631,7 +631,7 @@
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.7</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9550</v>
+        <v>9710</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+13.02%</t>
+          <t>'+14.91%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F3" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="G3" t="n">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>24748482440</v>
+        <v>26534479360</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170100</v>
+        <v>170400</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.73%</t>
+          <t>'+1.91%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G4" t="n">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="H4" t="n">
         <v>75.02</v>
@@ -794,7 +794,7 @@
         <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>519944914800</v>
+        <v>527650651050</v>
       </c>
       <c r="P4" t="n">
         <v>243500</v>
@@ -839,184 +839,184 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9080</v>
+        <v>216500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.78%</t>
+          <t>'+0.46%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>0.01</v>
       </c>
       <c r="E5" t="n">
-        <v>114</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>62</v>
+        <v>505</v>
       </c>
       <c r="G5" t="n">
-        <v>253</v>
+        <v>1653</v>
       </c>
       <c r="H5" t="n">
-        <v>1.74</v>
+        <v>45.99</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9010</v>
+        <v>215500</v>
       </c>
       <c r="K5" t="n">
-        <v>8810</v>
+        <v>207000</v>
       </c>
       <c r="L5" t="n">
-        <v>9500</v>
+        <v>219500</v>
       </c>
       <c r="M5" t="n">
-        <v>8510</v>
+        <v>206500</v>
       </c>
       <c r="N5" t="n">
-        <v>0.72</v>
+        <v>45.98</v>
       </c>
       <c r="O5" t="n">
-        <v>143255132505</v>
+        <v>2471588862250</v>
       </c>
       <c r="P5" t="n">
-        <v>9500</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>2270</v>
+        <v>94500</v>
       </c>
       <c r="R5" t="n">
-        <v>-230000</v>
+        <v>1544000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>729000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>HT로보틱스, 단기과열 및 투자경고 지정 예고. 분석글 게시 후 급락 가능성 언급.</t>
+          <t>외국인 순매수세 확인, 주주환원 시작으로 인한 단기 반등 기대감 존재. 정치적 이슈 언급 및 일부 부정적 전망 혼재.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['단기과열', '투자경고', '급락']</t>
+          <t>['외국인 순매수', '주주환원', '반등']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>216000</v>
+        <v>9050</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.44%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.01</v>
+        <v>1.02</v>
       </c>
       <c r="E6" t="n">
-        <v>800</v>
+        <v>116</v>
       </c>
       <c r="F6" t="n">
-        <v>508</v>
+        <v>64</v>
       </c>
       <c r="G6" t="n">
-        <v>1660</v>
+        <v>254</v>
       </c>
       <c r="H6" t="n">
-        <v>45.99</v>
+        <v>1.74</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>215500</v>
+        <v>9010</v>
       </c>
       <c r="K6" t="n">
-        <v>207000</v>
+        <v>8810</v>
       </c>
       <c r="L6" t="n">
-        <v>219500</v>
+        <v>9500</v>
       </c>
       <c r="M6" t="n">
-        <v>206500</v>
+        <v>8510</v>
       </c>
       <c r="N6" t="n">
-        <v>45.98</v>
+        <v>0.72</v>
       </c>
       <c r="O6" t="n">
-        <v>2422365952250</v>
+        <v>143995751820</v>
       </c>
       <c r="P6" t="n">
-        <v>374500</v>
+        <v>9500</v>
       </c>
       <c r="Q6" t="n">
-        <v>94500</v>
+        <v>2270</v>
       </c>
       <c r="R6" t="n">
-        <v>1544000</v>
+        <v>-230000</v>
       </c>
       <c r="S6" t="n">
-        <v>729000</v>
+        <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>이재명 관련 정치적 발언과 함께 금일 외국인 순매수 1위 확인. 일부는 금요일 바닥 다짐 후 주주환원 시작 및 나스닥 반도체주 상승에 따른 긍정적 전망 제시.</t>
+          <t>HT로보틱스, 단기과열 및 투자경고 지정 예고. 분석글 게시 후 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['외국인 순매수', '주주환원', '반도체주']</t>
+          <t>['단기과열', '투자경고', '급락']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -1038,13 +1038,13 @@
         <v>-0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F7" t="n">
         <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="H7" t="n">
         <v>9.699999999999999</v>
@@ -1070,7 +1070,7 @@
         <v>9.779999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>30534794965</v>
+        <v>31201259520</v>
       </c>
       <c r="P7" t="n">
         <v>40350</v>
@@ -1119,18 +1119,18 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14940</v>
+        <v>14950</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.07%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F8" t="n">
         <v>36</v>
@@ -1162,7 +1162,7 @@
         <v>0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>28770613845</v>
+        <v>28882493175</v>
       </c>
       <c r="P8" t="n">
         <v>30800</v>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1256000</v>
+        <v>1261000</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.26%</t>
+          <t>'-0.86%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1225,10 +1225,10 @@
         <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="G9" t="n">
-        <v>1763</v>
+        <v>1805</v>
       </c>
       <c r="H9" t="n">
         <v>48.82</v>
@@ -1254,7 +1254,7 @@
         <v>48.85</v>
       </c>
       <c r="O9" t="n">
-        <v>3149252380000</v>
+        <v>3212932278500</v>
       </c>
       <c r="P9" t="n">
         <v>2987000</v>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>금융감독원장이 SK하이닉스 자회사 솔리다임의 미국 중복상장이 규정 저촉 판단을 내림. 이는 솔리다임 상장 철회 가능성을 높이며, 해당 이슈가 주가에 긍정적 영향을 줄 것으로 전망.</t>
+          <t>솔리다임 중복상장 관련 금융감독원 규정 저촉 판단 속보. 상장 제동에 따른 호재성 재료로 작용하여 긍정적 전망 우세.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18070</v>
+        <v>18120</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.79%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1320,7 +1320,7 @@
         <v>41</v>
       </c>
       <c r="G10" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H10" t="n">
         <v>27.85</v>
@@ -1337,7 +1337,7 @@
         <v>17690</v>
       </c>
       <c r="L10" t="n">
-        <v>18110</v>
+        <v>18120</v>
       </c>
       <c r="M10" t="n">
         <v>17670</v>
@@ -1346,7 +1346,7 @@
         <v>27.77</v>
       </c>
       <c r="O10" t="n">
-        <v>38368523220</v>
+        <v>39347277575</v>
       </c>
       <c r="P10" t="n">
         <v>35350</v>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14120</v>
+        <v>14210</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.93%</t>
+          <t>'-5.33%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1412,7 +1412,7 @@
         <v>60</v>
       </c>
       <c r="G11" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>41908554900</v>
+        <v>42245635860</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1173</v>
+        <v>1178</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-6.98%</t>
+          <t>'-6.58%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F12" t="n">
         <v>29</v>
       </c>
       <c r="G12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>12070374712</v>
+        <v>12152483912</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>

--- a/data/trending_integrated_20261019_14.xlsx
+++ b/data/trending_integrated_20261019_14.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F2" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" t="n">
-        <v>621</v>
+        <v>628</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20605406252</v>
+        <v>20610412524</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 950톤 공급 사실 확인. 외인 매수세 유입되며 전고점 돌파 기대감 형성.</t>
+          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 950톤 공급 단독 기사 확인. 외인 매집 중이며 전고점 돌파 기대감 형성.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스페이스X', '강관', '납품']</t>
+          <t>['스페이스X', '강관', '외인 매집']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9710</v>
+        <v>10000</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+14.91%</t>
+          <t>'+18.34%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="F3" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="G3" t="n">
-        <v>230</v>
+        <v>254</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -693,7 +693,7 @@
         <v>9600</v>
       </c>
       <c r="L3" t="n">
-        <v>9880</v>
+        <v>10070</v>
       </c>
       <c r="M3" t="n">
         <v>9300</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>26534479360</v>
+        <v>31922219880</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -711,10 +711,10 @@
         <v>5390</v>
       </c>
       <c r="R3" t="n">
-        <v>-211000</v>
+        <v>-155000</v>
       </c>
       <c r="S3" t="n">
-        <v>5000</v>
+        <v>3000</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -747,70 +747,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>170400</v>
+        <v>15060</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+1.91%</t>
+          <t>'+0.74%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>52</v>
+        <v>36</v>
       </c>
       <c r="G4" t="n">
-        <v>268</v>
+        <v>93</v>
       </c>
       <c r="H4" t="n">
-        <v>75.02</v>
+        <v>0.06</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>167200</v>
+        <v>14950</v>
       </c>
       <c r="K4" t="n">
-        <v>159600</v>
+        <v>14610</v>
       </c>
       <c r="L4" t="n">
-        <v>175500</v>
+        <v>16600</v>
       </c>
       <c r="M4" t="n">
-        <v>159200</v>
+        <v>14610</v>
       </c>
       <c r="N4" t="n">
-        <v>75</v>
+        <v>0.11</v>
       </c>
       <c r="O4" t="n">
-        <v>527650651050</v>
+        <v>29033328370</v>
       </c>
       <c r="P4" t="n">
-        <v>243500</v>
+        <v>30800</v>
       </c>
       <c r="Q4" t="n">
-        <v>71000</v>
+        <v>9810</v>
       </c>
       <c r="R4" t="n">
-        <v>-73000</v>
+        <v>15000</v>
       </c>
       <c r="S4" t="n">
-        <v>-23000</v>
+        <v>2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
+          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['우선주', '주문실수', '외인매수']</t>
+          <t>['하이드로겔', '주문폭증', '신규주']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>216500</v>
+        <v>167700</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.46%</t>
+          <t>'+0.30%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>66</v>
       </c>
       <c r="F5" t="n">
-        <v>505</v>
+        <v>53</v>
       </c>
       <c r="G5" t="n">
-        <v>1653</v>
+        <v>264</v>
       </c>
       <c r="H5" t="n">
-        <v>45.99</v>
+        <v>75.02</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,367 +871,367 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>215500</v>
+        <v>167200</v>
       </c>
       <c r="K5" t="n">
-        <v>207000</v>
+        <v>159600</v>
       </c>
       <c r="L5" t="n">
-        <v>219500</v>
+        <v>175500</v>
       </c>
       <c r="M5" t="n">
-        <v>206500</v>
+        <v>159200</v>
       </c>
       <c r="N5" t="n">
-        <v>45.98</v>
+        <v>75</v>
       </c>
       <c r="O5" t="n">
-        <v>2471588862250</v>
+        <v>545467897950</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>243500</v>
       </c>
       <c r="Q5" t="n">
-        <v>94500</v>
+        <v>71000</v>
       </c>
       <c r="R5" t="n">
-        <v>1544000</v>
+        <v>-116000</v>
       </c>
       <c r="S5" t="n">
-        <v>729000</v>
+        <v>-21000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>외국인 순매수세 확인, 주주환원 시작으로 인한 단기 반등 기대감 존재. 정치적 이슈 언급 및 일부 부정적 전망 혼재.</t>
+          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['외국인 순매수', '주주환원', '반등']</t>
+          <t>['우선주', '주문실수', '외인매수']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>9050</v>
+        <v>14710</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.44%</t>
+          <t>'-0.14%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1.02</v>
+        <v>-0.08</v>
       </c>
       <c r="E6" t="n">
-        <v>116</v>
+        <v>147</v>
       </c>
       <c r="F6" t="n">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="G6" t="n">
-        <v>254</v>
+        <v>324</v>
       </c>
       <c r="H6" t="n">
-        <v>1.74</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>9010</v>
+        <v>14730</v>
       </c>
       <c r="K6" t="n">
-        <v>8810</v>
+        <v>14500</v>
       </c>
       <c r="L6" t="n">
-        <v>9500</v>
+        <v>15070</v>
       </c>
       <c r="M6" t="n">
-        <v>8510</v>
+        <v>14120</v>
       </c>
       <c r="N6" t="n">
-        <v>0.72</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>143995751820</v>
+        <v>31999435820</v>
       </c>
       <c r="P6" t="n">
-        <v>9500</v>
+        <v>40350</v>
       </c>
       <c r="Q6" t="n">
-        <v>2270</v>
+        <v>3320</v>
       </c>
       <c r="R6" t="n">
-        <v>-230000</v>
+        <v>-83000</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>-106000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>HT로보틱스, 단기과열 및 투자경고 지정 예고. 분석글 게시 후 급락 가능성 언급.</t>
+          <t>대우건설, 정치적 언급 및 주가 조작 의혹 관련 게시글 다수. 외인 보유율 관련 언급이 있으나 실질적인 주가 흐름에 대한 구체적 팩트 부족.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['단기과열', '투자경고', '급락']</t>
+          <t>['주가 조작', '외인 보유율', '뱅크런']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14760</v>
+        <v>8990</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.20%</t>
+          <t>'-0.22%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.08</v>
+        <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="G7" t="n">
-        <v>309</v>
+        <v>254</v>
       </c>
       <c r="H7" t="n">
-        <v>9.699999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14730</v>
+        <v>9010</v>
       </c>
       <c r="K7" t="n">
-        <v>14500</v>
+        <v>8810</v>
       </c>
       <c r="L7" t="n">
-        <v>15070</v>
+        <v>9500</v>
       </c>
       <c r="M7" t="n">
-        <v>14120</v>
+        <v>8510</v>
       </c>
       <c r="N7" t="n">
-        <v>9.779999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="O7" t="n">
-        <v>31201259520</v>
+        <v>145798428750</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>9500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>2270</v>
       </c>
       <c r="R7" t="n">
-        <v>-91000</v>
+        <v>-235000</v>
       </c>
       <c r="S7" t="n">
-        <v>-79000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>주가 조작 의혹 및 외인보유율 관련 논란.</t>
+          <t>HT로보틱스, 단기과열 및 투자경고 지정 예고. 분석글 게시 후 급락 가능성 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가조작', '외인보유율', '논란']</t>
+          <t>['단기과열', '투자경고', '급락']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14950</v>
+        <v>214750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.35%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>64</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>36</v>
+        <v>505</v>
       </c>
       <c r="G8" t="n">
-        <v>90</v>
+        <v>1629</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06</v>
+        <v>45.99</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14950</v>
+        <v>215500</v>
       </c>
       <c r="K8" t="n">
-        <v>14610</v>
+        <v>207000</v>
       </c>
       <c r="L8" t="n">
-        <v>16600</v>
+        <v>219500</v>
       </c>
       <c r="M8" t="n">
-        <v>14610</v>
+        <v>206500</v>
       </c>
       <c r="N8" t="n">
-        <v>0.11</v>
+        <v>45.98</v>
       </c>
       <c r="O8" t="n">
-        <v>28882493175</v>
+        <v>2571662783500</v>
       </c>
       <c r="P8" t="n">
-        <v>30800</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>9810</v>
+        <v>94500</v>
       </c>
       <c r="R8" t="n">
-        <v>20000</v>
+        <v>1564000</v>
       </c>
       <c r="S8" t="n">
-        <v>1000</v>
+        <v>718000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
+          <t>삼성전자, 개인 투자자들의 정치적 언급 및 혼조세 게시글 다수. 외국인 순매수가 일부 확인되었으나 전반적인 주가 하락세.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['하이드로겔', '주문폭증', '신규주']</t>
+          <t>['외국인 순매수', '바닥 다지기', '주주환원']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1261000</v>
+        <v>18100</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-0.86%</t>
+          <t>'-1.63%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.03</v>
+        <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>64</v>
       </c>
       <c r="F9" t="n">
-        <v>501</v>
+        <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>1805</v>
+        <v>223</v>
       </c>
       <c r="H9" t="n">
-        <v>48.82</v>
+        <v>27.85</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,91 +1239,91 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>1272000</v>
+        <v>18400</v>
       </c>
       <c r="K9" t="n">
-        <v>1212000</v>
+        <v>17690</v>
       </c>
       <c r="L9" t="n">
-        <v>1268000</v>
+        <v>18130</v>
       </c>
       <c r="M9" t="n">
-        <v>1208000</v>
+        <v>17670</v>
       </c>
       <c r="N9" t="n">
-        <v>48.85</v>
+        <v>27.77</v>
       </c>
       <c r="O9" t="n">
-        <v>3212932278500</v>
+        <v>40409401620</v>
       </c>
       <c r="P9" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q9" t="n">
-        <v>465500</v>
+        <v>17210</v>
       </c>
       <c r="R9" t="n">
-        <v>-13000</v>
+        <v>-633000</v>
       </c>
       <c r="S9" t="n">
-        <v>52000</v>
+        <v>6000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>솔리다임 중복상장 관련 금융감독원 규정 저촉 판단 속보. 상장 제동에 따른 호재성 재료로 작용하여 긍정적 전망 우세.</t>
+          <t>삼성중공업, 조선주 목표가 하향 조정 및 공매도 지속. 하락세 지속 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['솔리다임', '중복상장', '금감원']</t>
+          <t>['조선주', '공매도', '목표가']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18120</v>
+        <v>1245000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.52%</t>
+          <t>'-2.12%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.08</v>
+        <v>-0.03</v>
       </c>
       <c r="E10" t="n">
-        <v>64</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>41</v>
+        <v>500</v>
       </c>
       <c r="G10" t="n">
-        <v>221</v>
+        <v>1715</v>
       </c>
       <c r="H10" t="n">
-        <v>27.85</v>
+        <v>48.82</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,60 +1331,60 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>18400</v>
+        <v>1272000</v>
       </c>
       <c r="K10" t="n">
-        <v>17690</v>
+        <v>1212000</v>
       </c>
       <c r="L10" t="n">
-        <v>18120</v>
+        <v>1268000</v>
       </c>
       <c r="M10" t="n">
-        <v>17670</v>
+        <v>1208000</v>
       </c>
       <c r="N10" t="n">
-        <v>27.77</v>
+        <v>48.85</v>
       </c>
       <c r="O10" t="n">
-        <v>39347277575</v>
+        <v>3345065630500</v>
       </c>
       <c r="P10" t="n">
-        <v>35350</v>
+        <v>2987000</v>
       </c>
       <c r="Q10" t="n">
-        <v>17210</v>
+        <v>465500</v>
       </c>
       <c r="R10" t="n">
-        <v>-602000</v>
+        <v>-34000</v>
       </c>
       <c r="S10" t="n">
-        <v>-28000</v>
+        <v>39000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>삼성중공업, 조선주 목표가 하향 조정 및 공매도 지속. 하락세 지속 우려.</t>
+          <t>SK하이닉스, 솔리다임의 미국 중복상장 관련 논란 및 금감원 판단 내용 확인. 상장 철회 가능성에 대한 기대와 우려 공존.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['조선주', '공매도', '목표가']</t>
+          <t>['솔리다임', '중복상장', '금감원']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14210</v>
+        <v>14080</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.33%</t>
+          <t>'-6.20%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>42245635860</v>
+        <v>42578612985</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1447,7 +1447,7 @@
         <v>13610</v>
       </c>
       <c r="R11" t="n">
-        <v>32000</v>
+        <v>31000</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1487,21 +1487,21 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1178</v>
+        <v>1161</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-6.58%</t>
+          <t>'-7.93%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="F12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G12" t="n">
         <v>100</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>12152483912</v>
+        <v>12197876928</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>
@@ -1539,7 +1539,7 @@
         <v>192</v>
       </c>
       <c r="R12" t="n">
-        <v>-343000</v>
+        <v>-340000</v>
       </c>
       <c r="S12" t="n">
         <v>0</v>

--- a/data/trending_integrated_20261019_14.xlsx
+++ b/data/trending_integrated_20261019_14.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G2" t="n">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20610412524</v>
+        <v>20643766112</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>10000</v>
+        <v>9910</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+18.34%</t>
+          <t>'+17.28%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="F3" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>254</v>
+        <v>278</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>31922219880</v>
+        <v>35026914145</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -747,31 +747,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15060</v>
+        <v>9040</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.74%</t>
+          <t>'+0.33%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>-0.05</v>
+        <v>1.02</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>121</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>65</v>
       </c>
       <c r="G4" t="n">
-        <v>93</v>
+        <v>250</v>
       </c>
       <c r="H4" t="n">
-        <v>0.06</v>
+        <v>1.74</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
@@ -779,47 +779,47 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>14950</v>
+        <v>9010</v>
       </c>
       <c r="K4" t="n">
-        <v>14610</v>
+        <v>8810</v>
       </c>
       <c r="L4" t="n">
-        <v>16600</v>
+        <v>9500</v>
       </c>
       <c r="M4" t="n">
-        <v>14610</v>
+        <v>8510</v>
       </c>
       <c r="N4" t="n">
-        <v>0.11</v>
+        <v>0.72</v>
       </c>
       <c r="O4" t="n">
-        <v>29033328370</v>
+        <v>146742028895</v>
       </c>
       <c r="P4" t="n">
-        <v>30800</v>
+        <v>9500</v>
       </c>
       <c r="Q4" t="n">
-        <v>9810</v>
+        <v>2270</v>
       </c>
       <c r="R4" t="n">
-        <v>15000</v>
+        <v>-235000</v>
       </c>
       <c r="S4" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
+          <t>개인 투자자의 손실 경험 및 시장 불안감 언급. 분석글 이후 급락 경험 공유.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['하이드로겔', '주문폭증', '신규주']</t>
+          <t>['개인 투자', '시장 불안감', '급락']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -827,12 +827,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
@@ -854,13 +854,13 @@
         <v>0.02</v>
       </c>
       <c r="E5" t="n">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="F5" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G5" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="H5" t="n">
         <v>75.02</v>
@@ -886,7 +886,7 @@
         <v>75</v>
       </c>
       <c r="O5" t="n">
-        <v>545467897950</v>
+        <v>562730400750</v>
       </c>
       <c r="P5" t="n">
         <v>243500</v>
@@ -931,215 +931,215 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14710</v>
+        <v>14990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-0.14%</t>
+          <t>'+0.27%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="E6" t="n">
-        <v>147</v>
+        <v>69</v>
       </c>
       <c r="F6" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G6" t="n">
-        <v>324</v>
+        <v>93</v>
       </c>
       <c r="H6" t="n">
-        <v>9.699999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14730</v>
+        <v>14950</v>
       </c>
       <c r="K6" t="n">
-        <v>14500</v>
+        <v>14610</v>
       </c>
       <c r="L6" t="n">
-        <v>15070</v>
+        <v>16600</v>
       </c>
       <c r="M6" t="n">
-        <v>14120</v>
+        <v>14610</v>
       </c>
       <c r="N6" t="n">
-        <v>9.779999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="O6" t="n">
-        <v>31999435820</v>
+        <v>29129529135</v>
       </c>
       <c r="P6" t="n">
-        <v>40350</v>
+        <v>30800</v>
       </c>
       <c r="Q6" t="n">
-        <v>3320</v>
+        <v>9810</v>
       </c>
       <c r="R6" t="n">
-        <v>-83000</v>
+        <v>15000</v>
       </c>
       <c r="S6" t="n">
-        <v>-106000</v>
+        <v>2000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>대우건설, 정치적 언급 및 주가 조작 의혹 관련 게시글 다수. 외인 보유율 관련 언급이 있으나 실질적인 주가 흐름에 대한 구체적 팩트 부족.</t>
+          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['주가 조작', '외인 보유율', '뱅크런']</t>
+          <t>['하이드로겔', '주문폭증', '신규주']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>8990</v>
+        <v>215500</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-0.22%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1.02</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>118</v>
+        <v>800</v>
       </c>
       <c r="F7" t="n">
-        <v>65</v>
+        <v>512</v>
       </c>
       <c r="G7" t="n">
-        <v>254</v>
+        <v>1652</v>
       </c>
       <c r="H7" t="n">
-        <v>1.74</v>
+        <v>45.99</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>9010</v>
+        <v>215500</v>
       </c>
       <c r="K7" t="n">
-        <v>8810</v>
+        <v>207000</v>
       </c>
       <c r="L7" t="n">
-        <v>9500</v>
+        <v>219500</v>
       </c>
       <c r="M7" t="n">
-        <v>8510</v>
+        <v>206500</v>
       </c>
       <c r="N7" t="n">
-        <v>0.72</v>
+        <v>45.98</v>
       </c>
       <c r="O7" t="n">
-        <v>145798428750</v>
+        <v>2664136498750</v>
       </c>
       <c r="P7" t="n">
-        <v>9500</v>
+        <v>374500</v>
       </c>
       <c r="Q7" t="n">
-        <v>2270</v>
+        <v>94500</v>
       </c>
       <c r="R7" t="n">
-        <v>-235000</v>
+        <v>1564000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>718000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>HT로보틱스, 단기과열 및 투자경고 지정 예고. 분석글 게시 후 급락 가능성 언급.</t>
+          <t>악재 반영 완료 및 바닥 다지기 시그널 언급. 외국인 순매수 1위 기록.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['단기과열', '투자경고', '급락']</t>
+          <t>['외국인 순매수', '바닥 다지기', '상승 시그널']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>214750</v>
+        <v>14730</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.35%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>151</v>
       </c>
       <c r="F8" t="n">
-        <v>505</v>
+        <v>46</v>
       </c>
       <c r="G8" t="n">
-        <v>1629</v>
+        <v>329</v>
       </c>
       <c r="H8" t="n">
-        <v>45.99</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,47 +1147,47 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>215500</v>
+        <v>14730</v>
       </c>
       <c r="K8" t="n">
-        <v>207000</v>
+        <v>14500</v>
       </c>
       <c r="L8" t="n">
-        <v>219500</v>
+        <v>15070</v>
       </c>
       <c r="M8" t="n">
-        <v>206500</v>
+        <v>14120</v>
       </c>
       <c r="N8" t="n">
-        <v>45.98</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>2571662783500</v>
+        <v>32578069645</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>1564000</v>
+        <v>-83000</v>
       </c>
       <c r="S8" t="n">
-        <v>718000</v>
+        <v>-106000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성전자, 개인 투자자들의 정치적 언급 및 혼조세 게시글 다수. 외국인 순매수가 일부 확인되었으나 전반적인 주가 하락세.</t>
+          <t>대우건설, 정치적 언급 및 주가 조작 의혹 관련 게시글 다수. 외인 보유율 관련 언급이 있으나 실질적인 주가 흐름에 대한 구체적 팩트 부족.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['외국인 순매수', '바닥 다지기', '주주환원']</t>
+          <t>['주가 조작', '외인 보유율', '뱅크런']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -1211,18 +1211,18 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18100</v>
+        <v>18140</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.63%</t>
+          <t>'-1.41%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F9" t="n">
         <v>41</v>
@@ -1245,7 +1245,7 @@
         <v>17690</v>
       </c>
       <c r="L9" t="n">
-        <v>18130</v>
+        <v>18150</v>
       </c>
       <c r="M9" t="n">
         <v>17670</v>
@@ -1254,7 +1254,7 @@
         <v>27.77</v>
       </c>
       <c r="O9" t="n">
-        <v>40409401620</v>
+        <v>41594114525</v>
       </c>
       <c r="P9" t="n">
         <v>35350</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1245000</v>
+        <v>1246000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.12%</t>
+          <t>'-2.04%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="G10" t="n">
-        <v>1715</v>
+        <v>1679</v>
       </c>
       <c r="H10" t="n">
         <v>48.82</v>
@@ -1346,7 +1346,7 @@
         <v>48.85</v>
       </c>
       <c r="O10" t="n">
-        <v>3345065630500</v>
+        <v>3505089543000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,12 +1362,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>SK하이닉스, 솔리다임의 미국 중복상장 관련 논란 및 금감원 판단 내용 확인. 상장 철회 가능성에 대한 기대와 우려 공존.</t>
+          <t>솔리다임 중복상장 관련 금감원 판단 및 유권해석 대기 소식. 중복상장 저촉 판단으로 상장 철회 가능성 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
@@ -1395,11 +1395,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14080</v>
+        <v>14060</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-6.20%</t>
+          <t>'-6.33%</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>42578612985</v>
+        <v>42806713125</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1161</v>
+        <v>1168</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.93%</t>
+          <t>'-7.38%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>12197876928</v>
+        <v>12213679725</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>

--- a/data/trending_integrated_20261019_14.xlsx
+++ b/data/trending_integrated_20261019_14.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="F2" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G2" t="n">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20643766112</v>
+        <v>20652083096</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -626,7 +626,7 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>KBI동양철관, 스페이스X 로켓 발사대 강관 950톤 공급 단독 기사 확인. 외인 매집 중이며 전고점 돌파 기대감 형성.</t>
+          <t>스페이스X 로켓 발사대 강관 공급 단독 뉴스 기반으로 급등세. 외인 매수세 유입되며 전고점 돌파 기대.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
@@ -635,7 +635,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['스페이스X', '강관', '외인 매집']</t>
+          <t>['스페이스X', '강관', '납품']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,11 +659,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9910</v>
+        <v>9840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+17.28%</t>
+          <t>'+16.45%</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -676,7 +676,7 @@
         <v>75</v>
       </c>
       <c r="G3" t="n">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>35026914145</v>
+        <v>36747447290</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -747,307 +747,307 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9040</v>
+        <v>168100</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.33%</t>
+          <t>'+0.54%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1.02</v>
+        <v>0.02</v>
       </c>
       <c r="E4" t="n">
-        <v>121</v>
+        <v>78</v>
       </c>
       <c r="F4" t="n">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="G4" t="n">
-        <v>250</v>
+        <v>292</v>
       </c>
       <c r="H4" t="n">
-        <v>1.74</v>
+        <v>75.02</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>9010</v>
+        <v>167200</v>
       </c>
       <c r="K4" t="n">
-        <v>8810</v>
+        <v>159600</v>
       </c>
       <c r="L4" t="n">
-        <v>9500</v>
+        <v>175500</v>
       </c>
       <c r="M4" t="n">
-        <v>8510</v>
+        <v>159200</v>
       </c>
       <c r="N4" t="n">
-        <v>0.72</v>
+        <v>75</v>
       </c>
       <c r="O4" t="n">
-        <v>146742028895</v>
+        <v>575590191550</v>
       </c>
       <c r="P4" t="n">
-        <v>9500</v>
+        <v>243500</v>
       </c>
       <c r="Q4" t="n">
-        <v>2270</v>
+        <v>71000</v>
       </c>
       <c r="R4" t="n">
-        <v>-235000</v>
+        <v>-116000</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>-21000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>개인 투자자의 손실 경험 및 시장 불안감 언급. 분석글 이후 급락 경험 공유.</t>
+          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['개인 투자', '시장 불안감', '급락']</t>
+          <t>['우선주', '주문실수', '외인매수']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>167700</v>
+        <v>9050</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.30%</t>
+          <t>'+0.44%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.02</v>
+        <v>1.02</v>
       </c>
       <c r="E5" t="n">
-        <v>75</v>
+        <v>124</v>
       </c>
       <c r="F5" t="n">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="G5" t="n">
-        <v>278</v>
+        <v>254</v>
       </c>
       <c r="H5" t="n">
-        <v>75.02</v>
+        <v>1.74</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>167200</v>
+        <v>9010</v>
       </c>
       <c r="K5" t="n">
-        <v>159600</v>
+        <v>8810</v>
       </c>
       <c r="L5" t="n">
-        <v>175500</v>
+        <v>9500</v>
       </c>
       <c r="M5" t="n">
-        <v>159200</v>
+        <v>8510</v>
       </c>
       <c r="N5" t="n">
-        <v>75</v>
+        <v>0.72</v>
       </c>
       <c r="O5" t="n">
-        <v>562730400750</v>
+        <v>147446679530</v>
       </c>
       <c r="P5" t="n">
-        <v>243500</v>
+        <v>9500</v>
       </c>
       <c r="Q5" t="n">
-        <v>71000</v>
+        <v>2270</v>
       </c>
       <c r="R5" t="n">
-        <v>-116000</v>
+        <v>-235000</v>
       </c>
       <c r="S5" t="n">
-        <v>-21000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
+          <t>개인 투자자의 손실 경험 및 시장 불안감 언급. 분석글 이후 급락 경험 공유.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['우선주', '주문실수', '외인매수']</t>
+          <t>['개인 투자', '시장 불안감', '급락']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14990</v>
+        <v>216000</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.27%</t>
+          <t>'+0.23%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.05</v>
+        <v>0.01</v>
       </c>
       <c r="E6" t="n">
-        <v>69</v>
+        <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>37</v>
+        <v>512</v>
       </c>
       <c r="G6" t="n">
-        <v>93</v>
+        <v>1710</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06</v>
+        <v>45.99</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>14950</v>
+        <v>215500</v>
       </c>
       <c r="K6" t="n">
-        <v>14610</v>
+        <v>207000</v>
       </c>
       <c r="L6" t="n">
-        <v>16600</v>
+        <v>219500</v>
       </c>
       <c r="M6" t="n">
-        <v>14610</v>
+        <v>206500</v>
       </c>
       <c r="N6" t="n">
-        <v>0.11</v>
+        <v>45.98</v>
       </c>
       <c r="O6" t="n">
-        <v>29129529135</v>
+        <v>2728200069750</v>
       </c>
       <c r="P6" t="n">
-        <v>30800</v>
+        <v>374500</v>
       </c>
       <c r="Q6" t="n">
-        <v>9810</v>
+        <v>94500</v>
       </c>
       <c r="R6" t="n">
-        <v>15000</v>
+        <v>1564000</v>
       </c>
       <c r="S6" t="n">
-        <v>2000</v>
+        <v>718000</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
+          <t>악재 반영 완료 및 바닥 다지기 후 상승 전환 기대감. 외국인 순매수 소식 및 주주환원 정책 언급.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['하이드로겔', '주문폭증', '신규주']</t>
+          <t>['삼성전자', '외국인', '주주환원']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>추적</t>
+          <t>활성</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>215500</v>
+        <v>14760</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'+0.20%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>-0.08</v>
       </c>
       <c r="E7" t="n">
-        <v>800</v>
+        <v>152</v>
       </c>
       <c r="F7" t="n">
-        <v>512</v>
+        <v>46</v>
       </c>
       <c r="G7" t="n">
-        <v>1652</v>
+        <v>334</v>
       </c>
       <c r="H7" t="n">
-        <v>45.99</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,47 +1055,47 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>215500</v>
+        <v>14730</v>
       </c>
       <c r="K7" t="n">
-        <v>207000</v>
+        <v>14500</v>
       </c>
       <c r="L7" t="n">
-        <v>219500</v>
+        <v>15070</v>
       </c>
       <c r="M7" t="n">
-        <v>206500</v>
+        <v>14120</v>
       </c>
       <c r="N7" t="n">
-        <v>45.98</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>2664136498750</v>
+        <v>33342108915</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>94500</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>1564000</v>
+        <v>-83000</v>
       </c>
       <c r="S7" t="n">
-        <v>718000</v>
+        <v>-106000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>악재 반영 완료 및 바닥 다지기 시그널 언급. 외국인 순매수 1위 기록.</t>
+          <t>대우건설, 정치적 언급 및 주가 조작 의혹 관련 게시글 다수. 외인 보유율 관련 언급이 있으나 실질적인 주가 흐름에 대한 구체적 팩트 부족.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['외국인 순매수', '바닥 다지기', '상승 시그널']</t>
+          <t>['주가 조작', '외인 보유율', '뱅크런']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1108,99 +1108,99 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14730</v>
+        <v>14910</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'+0.00%</t>
+          <t>'-0.27%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.08</v>
+        <v>-0.05</v>
       </c>
       <c r="E8" t="n">
-        <v>151</v>
+        <v>66</v>
       </c>
       <c r="F8" t="n">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="G8" t="n">
-        <v>329</v>
+        <v>86</v>
       </c>
       <c r="H8" t="n">
-        <v>9.699999999999999</v>
+        <v>0.06</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14730</v>
+        <v>14950</v>
       </c>
       <c r="K8" t="n">
-        <v>14500</v>
+        <v>14610</v>
       </c>
       <c r="L8" t="n">
-        <v>15070</v>
+        <v>16600</v>
       </c>
       <c r="M8" t="n">
-        <v>14120</v>
+        <v>14610</v>
       </c>
       <c r="N8" t="n">
-        <v>9.779999999999999</v>
+        <v>0.11</v>
       </c>
       <c r="O8" t="n">
-        <v>32578069645</v>
+        <v>29369354255</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>30800</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>9810</v>
       </c>
       <c r="R8" t="n">
-        <v>-83000</v>
+        <v>15000</v>
       </c>
       <c r="S8" t="n">
-        <v>-106000</v>
+        <v>2000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대우건설, 정치적 언급 및 주가 조작 의혹 관련 게시글 다수. 외인 보유율 관련 언급이 있으나 실질적인 주가 흐름에 대한 구체적 팩트 부족.</t>
+          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['주가 조작', '외인 보유율', '뱅크런']</t>
+          <t>['하이드로겔', '주문폭증', '신규주']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>활성</t>
+          <t>추적</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
@@ -1211,11 +1211,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18140</v>
+        <v>18190</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.41%</t>
+          <t>'-1.14%</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -1228,7 +1228,7 @@
         <v>41</v>
       </c>
       <c r="G9" t="n">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H9" t="n">
         <v>27.85</v>
@@ -1245,7 +1245,7 @@
         <v>17690</v>
       </c>
       <c r="L9" t="n">
-        <v>18150</v>
+        <v>18200</v>
       </c>
       <c r="M9" t="n">
         <v>17670</v>
@@ -1254,7 +1254,7 @@
         <v>27.77</v>
       </c>
       <c r="O9" t="n">
-        <v>41594114525</v>
+        <v>42489124260</v>
       </c>
       <c r="P9" t="n">
         <v>35350</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1246000</v>
+        <v>1248000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.04%</t>
+          <t>'-1.89%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="G10" t="n">
-        <v>1679</v>
+        <v>1682</v>
       </c>
       <c r="H10" t="n">
         <v>48.82</v>
@@ -1346,7 +1346,7 @@
         <v>48.85</v>
       </c>
       <c r="O10" t="n">
-        <v>3505089543000</v>
+        <v>3576104557500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>솔리다임 중복상장 관련 금감원 판단 및 유권해석 대기 소식. 중복상장 저촉 판단으로 상장 철회 가능성 제기.</t>
+          <t>자회사 솔리다임의 미국 중복 상장 이슈로 인한 금감원 규정 저촉 판단. 주가 하락세 지속 및 투자자 손실 우려.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['솔리다임', '중복상장', '금감원']</t>
+          <t>['SK하이닉스', '솔리다임', '중복상장']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,18 +1395,18 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14060</v>
+        <v>14080</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-6.33%</t>
+          <t>'-6.20%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F11" t="n">
         <v>61</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>42806713125</v>
+        <v>43069798865</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1168</v>
+        <v>1158</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-7.38%</t>
+          <t>'-8.17%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="F12" t="n">
         <v>31</v>
       </c>
       <c r="G12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>12213679725</v>
+        <v>12281454528</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>

--- a/data/trending_integrated_20261019_14.xlsx
+++ b/data/trending_integrated_20261019_14.xlsx
@@ -578,13 +578,13 @@
         <v>0.42</v>
       </c>
       <c r="E2" t="n">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F2" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="G2" t="n">
-        <v>659</v>
+        <v>677</v>
       </c>
       <c r="H2" t="n">
         <v>0.83</v>
@@ -610,7 +610,7 @@
         <v>0.41</v>
       </c>
       <c r="O2" t="n">
-        <v>20652083096</v>
+        <v>20662810572</v>
       </c>
       <c r="P2" t="n">
         <v>2970</v>
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9840</v>
+        <v>9920</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+16.45%</t>
+          <t>'+17.40%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.16</v>
       </c>
       <c r="E3" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="F3" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G3" t="n">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="H3" t="n">
         <v>6.15</v>
@@ -702,7 +702,7 @@
         <v>5.99</v>
       </c>
       <c r="O3" t="n">
-        <v>36747447290</v>
+        <v>37843425315</v>
       </c>
       <c r="P3" t="n">
         <v>14940</v>
@@ -747,70 +747,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>진코스텍</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>168100</v>
+        <v>15060</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+0.54%</t>
+          <t>'+0.74%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.02</v>
+        <v>-0.05</v>
       </c>
       <c r="E4" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="F4" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>292</v>
+        <v>87</v>
       </c>
       <c r="H4" t="n">
-        <v>75.02</v>
+        <v>0.06</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>167200</v>
+        <v>14950</v>
       </c>
       <c r="K4" t="n">
-        <v>159600</v>
+        <v>14610</v>
       </c>
       <c r="L4" t="n">
-        <v>175500</v>
+        <v>16600</v>
       </c>
       <c r="M4" t="n">
-        <v>159200</v>
+        <v>14610</v>
       </c>
       <c r="N4" t="n">
-        <v>75</v>
+        <v>0.11</v>
       </c>
       <c r="O4" t="n">
-        <v>575590191550</v>
+        <v>29488883835</v>
       </c>
       <c r="P4" t="n">
-        <v>243500</v>
+        <v>30800</v>
       </c>
       <c r="Q4" t="n">
-        <v>71000</v>
+        <v>9810</v>
       </c>
       <c r="R4" t="n">
-        <v>-116000</v>
+        <v>15000</v>
       </c>
       <c r="S4" t="n">
-        <v>-21000</v>
+        <v>2000</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
+          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,11 +819,11 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['우선주', '주문실수', '외인매수']</t>
+          <t>['하이드로겔', '주문폭증', '신규주']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,77 +832,77 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>005935</t>
+          <t>250030</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>HT로보틱스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9050</v>
+        <v>14740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+0.44%</t>
+          <t>'+0.07%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1.02</v>
+        <v>-0.08</v>
       </c>
       <c r="E5" t="n">
-        <v>124</v>
+        <v>154</v>
       </c>
       <c r="F5" t="n">
-        <v>67</v>
+        <v>46</v>
       </c>
       <c r="G5" t="n">
-        <v>254</v>
+        <v>337</v>
       </c>
       <c r="H5" t="n">
-        <v>1.74</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>9010</v>
+        <v>14730</v>
       </c>
       <c r="K5" t="n">
-        <v>8810</v>
+        <v>14500</v>
       </c>
       <c r="L5" t="n">
-        <v>9500</v>
+        <v>15070</v>
       </c>
       <c r="M5" t="n">
-        <v>8510</v>
+        <v>14120</v>
       </c>
       <c r="N5" t="n">
-        <v>0.72</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>147446679530</v>
+        <v>33862574815</v>
       </c>
       <c r="P5" t="n">
-        <v>9500</v>
+        <v>40350</v>
       </c>
       <c r="Q5" t="n">
-        <v>2270</v>
+        <v>3320</v>
       </c>
       <c r="R5" t="n">
-        <v>-235000</v>
+        <v>-83000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>-106000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>개인 투자자의 손실 경험 및 시장 불안감 언급. 분석글 이후 급락 경험 공유.</t>
+          <t>대우건설, 정치적 언급 및 주가 조작 의혹 관련 게시글 다수. 외인 보유율 관련 언급이 있으나 실질적인 주가 흐름에 대한 구체적 팩트 부족.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['개인 투자', '시장 불안감', '급락']</t>
+          <t>['주가 조작', '외인 보유율', '뱅크런']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>396300</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
@@ -935,11 +935,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>216000</v>
+        <v>215500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+0.23%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -949,10 +949,10 @@
         <v>800</v>
       </c>
       <c r="F6" t="n">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="G6" t="n">
-        <v>1710</v>
+        <v>1723</v>
       </c>
       <c r="H6" t="n">
         <v>45.99</v>
@@ -978,7 +978,7 @@
         <v>45.98</v>
       </c>
       <c r="O6" t="n">
-        <v>2728200069750</v>
+        <v>2789330469250</v>
       </c>
       <c r="P6" t="n">
         <v>374500</v>
@@ -994,7 +994,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>악재 반영 완료 및 바닥 다지기 후 상승 전환 기대감. 외국인 순매수 소식 및 주주환원 정책 언급.</t>
+          <t>삼성전자, 외국인 순매수 1위 기록 및 주주환원 시작 예고. 다만, 시장의 급등락 및 개인 투자자들의 혼조세 관찰됨.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['삼성전자', '외국인', '주주환원']</t>
+          <t>['외국인 순매수', '주주환원', '시장 전망']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,83 +1023,83 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>HT로보틱스</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14760</v>
+        <v>9010</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+0.20%</t>
+          <t>'+0.00%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.08</v>
+        <v>1.02</v>
       </c>
       <c r="E7" t="n">
-        <v>152</v>
+        <v>125</v>
       </c>
       <c r="F7" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
-        <v>334</v>
+        <v>261</v>
       </c>
       <c r="H7" t="n">
-        <v>9.699999999999999</v>
+        <v>1.74</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>14730</v>
+        <v>9010</v>
       </c>
       <c r="K7" t="n">
-        <v>14500</v>
+        <v>8810</v>
       </c>
       <c r="L7" t="n">
-        <v>15070</v>
+        <v>9500</v>
       </c>
       <c r="M7" t="n">
-        <v>14120</v>
+        <v>8510</v>
       </c>
       <c r="N7" t="n">
-        <v>9.779999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="O7" t="n">
-        <v>33342108915</v>
+        <v>148097710610</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>9500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>2270</v>
       </c>
       <c r="R7" t="n">
-        <v>-83000</v>
+        <v>-235000</v>
       </c>
       <c r="S7" t="n">
-        <v>-106000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대우건설, 정치적 언급 및 주가 조작 의혹 관련 게시글 다수. 외인 보유율 관련 언급이 있으나 실질적인 주가 흐름에 대한 구체적 팩트 부족.</t>
+          <t>HT로보틱스, 시장 전반의 하락세 속에서 특별한 근거 없이 개인 투자자들의 혼란과 손실 경험이 주로 언급됨.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['주가 조작', '외인 보유율', '뱅크런']</t>
+          <t>['로봇주', '개인 투자', '시장']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,77 +1108,77 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>396300</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>진코스텍</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14910</v>
+        <v>166900</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-0.27%</t>
+          <t>'-0.18%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.05</v>
+        <v>0.02</v>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="F8" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="G8" t="n">
-        <v>86</v>
+        <v>295</v>
       </c>
       <c r="H8" t="n">
-        <v>0.06</v>
+        <v>75.02</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>14950</v>
+        <v>167200</v>
       </c>
       <c r="K8" t="n">
-        <v>14610</v>
+        <v>159600</v>
       </c>
       <c r="L8" t="n">
-        <v>16600</v>
+        <v>175500</v>
       </c>
       <c r="M8" t="n">
-        <v>14610</v>
+        <v>159200</v>
       </c>
       <c r="N8" t="n">
-        <v>0.11</v>
+        <v>75</v>
       </c>
       <c r="O8" t="n">
-        <v>29369354255</v>
+        <v>588490521400</v>
       </c>
       <c r="P8" t="n">
-        <v>30800</v>
+        <v>243500</v>
       </c>
       <c r="Q8" t="n">
-        <v>9810</v>
+        <v>71000</v>
       </c>
       <c r="R8" t="n">
-        <v>15000</v>
+        <v>-116000</v>
       </c>
       <c r="S8" t="n">
-        <v>2000</v>
+        <v>-21000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>진코스텍, 하이드로겔 주문 폭증으로 생산능력 초과. 신규 주문 처리 난항. 제2의 에이피알 기대감.</t>
+          <t>삼성전자우, 주문 실수 논란 속 급등. 외인 매수세 동반.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,11 +1187,11 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['하이드로겔', '주문폭증', '신규주']</t>
+          <t>['우선주', '주문실수', '외인매수']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>250030</t>
+          <t>005935</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18190</v>
+        <v>18180</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.14%</t>
+          <t>'-1.20%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>0.08</v>
       </c>
       <c r="E9" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F9" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G9" t="n">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="H9" t="n">
         <v>27.85</v>
@@ -1254,7 +1254,7 @@
         <v>27.77</v>
       </c>
       <c r="O9" t="n">
-        <v>42489124260</v>
+        <v>43482022005</v>
       </c>
       <c r="P9" t="n">
         <v>35350</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1248000</v>
+        <v>1247000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.89%</t>
+          <t>'-1.97%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>491</v>
+        <v>496</v>
       </c>
       <c r="G10" t="n">
-        <v>1682</v>
+        <v>1717</v>
       </c>
       <c r="H10" t="n">
         <v>48.82</v>
@@ -1346,7 +1346,7 @@
         <v>48.85</v>
       </c>
       <c r="O10" t="n">
-        <v>3576104557500</v>
+        <v>3641035525000</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>자회사 솔리다임의 미국 중복 상장 이슈로 인한 금감원 규정 저촉 판단. 주가 하락세 지속 및 투자자 손실 우려.</t>
+          <t>SK하이닉스, 솔리다임의 중복상장 관련 논란 지속. 금감원 판단 및 규정 저촉 여부에 대한 투자자들의 우려와 부정적 전망 나타남.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['SK하이닉스', '솔리다임', '중복상장']</t>
+          <t>['솔리다임', '중복상장', '금감원']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14080</v>
+        <v>14060</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-6.20%</t>
+          <t>'-6.33%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F11" t="n">
         <v>61</v>
       </c>
       <c r="G11" t="n">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="H11" t="n">
         <v>0</v>
@@ -1438,7 +1438,7 @@
         <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>43069798865</v>
+        <v>43438537695</v>
       </c>
       <c r="P11" t="n">
         <v>28800</v>
@@ -1487,24 +1487,24 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1158</v>
+        <v>1156</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-8.17%</t>
+          <t>'-8.33%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F12" t="n">
         <v>31</v>
       </c>
       <c r="G12" t="n">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -1530,7 +1530,7 @@
         <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>12281454528</v>
+        <v>12328448562</v>
       </c>
       <c r="P12" t="n">
         <v>1950</v>
